--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-09-2025.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£15.74</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£33.99</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£40.28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
